--- a/InputData/plcy-schd/V/Vintage.xlsx
+++ b/InputData/plcy-schd/V/Vintage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\plcy-schd\V\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\plcy-schd\V\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2012DEE9-22D9-47AF-8795-7E4F8E3ED039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD24F716-DF92-4A8B-9F59-A270CC7C5B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="27270" windowHeight="16395" activeTab="5" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="FV" sheetId="4" r:id="rId3"/>
     <sheet name="CV" sheetId="6" r:id="rId4"/>
     <sheet name="PV" sheetId="7" r:id="rId5"/>
+    <sheet name="HV" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Source: None</t>
   </si>
@@ -70,6 +71,12 @@
   </si>
   <si>
     <t>Preceding Vintage</t>
+  </si>
+  <si>
+    <t>Historical Vintage</t>
+  </si>
+  <si>
+    <t>Vintage1950</t>
   </si>
 </sst>
 </file>
@@ -4156,4 +4163,579 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86911333-B772-4AEC-92FF-4B2FC3210B72}">
+  <sheetPr>
+    <tabColor theme="3" tint="9.9978637043366805E-2"/>
+  </sheetPr>
+  <dimension ref="A1:A94"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f>V!A3</f>
+        <v>Vintage1951</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <f>V!A4</f>
+        <v>Vintage1952</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <f>V!A5</f>
+        <v>Vintage1953</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f>V!A6</f>
+        <v>Vintage1954</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f>V!A7</f>
+        <v>Vintage1955</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f>V!A8</f>
+        <v>Vintage1956</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f>V!A9</f>
+        <v>Vintage1957</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f>V!A10</f>
+        <v>Vintage1958</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f>V!A11</f>
+        <v>Vintage1959</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f>V!A12</f>
+        <v>Vintage1960</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f>V!A13</f>
+        <v>Vintage1961</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f>V!A14</f>
+        <v>Vintage1962</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f>V!A15</f>
+        <v>Vintage1963</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f>V!A16</f>
+        <v>Vintage1964</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f>V!A17</f>
+        <v>Vintage1965</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f>V!A18</f>
+        <v>Vintage1966</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f>V!A19</f>
+        <v>Vintage1967</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <f>V!A20</f>
+        <v>Vintage1968</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f>V!A21</f>
+        <v>Vintage1969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f>V!A22</f>
+        <v>Vintage1970</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f>V!A23</f>
+        <v>Vintage1971</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f>V!A24</f>
+        <v>Vintage1972</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f>V!A25</f>
+        <v>Vintage1973</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <f>V!A26</f>
+        <v>Vintage1974</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <f>V!A27</f>
+        <v>Vintage1975</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <f>V!A28</f>
+        <v>Vintage1976</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="str">
+        <f>V!A29</f>
+        <v>Vintage1977</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <f>V!A30</f>
+        <v>Vintage1978</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
+        <f>V!A31</f>
+        <v>Vintage1979</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="str">
+        <f>V!A32</f>
+        <v>Vintage1980</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f>V!A33</f>
+        <v>Vintage1981</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f>V!A34</f>
+        <v>Vintage1982</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f>V!A35</f>
+        <v>Vintage1983</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f>V!A36</f>
+        <v>Vintage1984</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <f>V!A37</f>
+        <v>Vintage1985</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <f>V!A38</f>
+        <v>Vintage1986</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f>V!A39</f>
+        <v>Vintage1987</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <f>V!A40</f>
+        <v>Vintage1988</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="str">
+        <f>V!A41</f>
+        <v>Vintage1989</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="str">
+        <f>V!A42</f>
+        <v>Vintage1990</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
+        <f>V!A43</f>
+        <v>Vintage1991</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="str">
+        <f>V!A44</f>
+        <v>Vintage1992</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="str">
+        <f>V!A45</f>
+        <v>Vintage1993</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="str">
+        <f>V!A46</f>
+        <v>Vintage1994</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="str">
+        <f>V!A47</f>
+        <v>Vintage1995</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="str">
+        <f>V!A48</f>
+        <v>Vintage1996</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="str">
+        <f>V!A49</f>
+        <v>Vintage1997</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="str">
+        <f>V!A50</f>
+        <v>Vintage1998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="str">
+        <f>V!A51</f>
+        <v>Vintage1999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="str">
+        <f>V!A52</f>
+        <v>Vintage2000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="str">
+        <f>V!A53</f>
+        <v>Vintage2001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="str">
+        <f>V!A54</f>
+        <v>Vintage2002</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="str">
+        <f>V!A55</f>
+        <v>Vintage2003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="str">
+        <f>V!A56</f>
+        <v>Vintage2004</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="str">
+        <f>V!A57</f>
+        <v>Vintage2005</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="str">
+        <f>V!A58</f>
+        <v>Vintage2006</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="str">
+        <f>V!A59</f>
+        <v>Vintage2007</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="str">
+        <f>V!A60</f>
+        <v>Vintage2008</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="str">
+        <f>V!A61</f>
+        <v>Vintage2009</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="str">
+        <f>V!A62</f>
+        <v>Vintage2010</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="str">
+        <f>V!A63</f>
+        <v>Vintage2011</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="str">
+        <f>V!A64</f>
+        <v>Vintage2012</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="str">
+        <f>V!A65</f>
+        <v>Vintage2013</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="str">
+        <f>V!A66</f>
+        <v>Vintage2014</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="str">
+        <f>V!A67</f>
+        <v>Vintage2015</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="str">
+        <f>V!A68</f>
+        <v>Vintage2016</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="str">
+        <f>V!A69</f>
+        <v>Vintage2017</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="str">
+        <f>V!A70</f>
+        <v>Vintage2018</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="str">
+        <f>V!A71</f>
+        <v>Vintage2019</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="str">
+        <f>V!A72</f>
+        <v>Vintage2020</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="str">
+        <f>V!A153</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="str">
+        <f>V!A154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="str">
+        <f>V!A155</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="str">
+        <f>V!A156</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="str">
+        <f>V!A157</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="str">
+        <f>V!A158</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="str">
+        <f>V!A159</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="str">
+        <f>V!A160</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="str">
+        <f>V!A161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="str">
+        <f>V!A162</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="str">
+        <f>V!A163</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="str">
+        <f>V!A164</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="str">
+        <f>V!A165</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="str">
+        <f>V!A166</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="str">
+        <f>V!A167</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="str">
+        <f>V!A168</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="str">
+        <f>V!A169</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="str">
+        <f>V!A170</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="str">
+        <f>V!A171</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="str">
+        <f>V!A172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="str">
+        <f>V!A173</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="str">
+        <f>V!A174</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/InputData/plcy-schd/V/Vintage.xlsx
+++ b/InputData/plcy-schd/V/Vintage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\plcy-schd\V\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD24F716-DF92-4A8B-9F59-A270CC7C5B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7A55AB-7E12-459F-B36D-DB5D5E1386B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="27270" windowHeight="16395" activeTab="5" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11175" activeTab="1" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -516,7 +516,7 @@
   <sheetPr>
     <tabColor theme="3" tint="9.9978637043366805E-2"/>
   </sheetPr>
-  <dimension ref="A1:A174"/>
+  <dimension ref="A1:A152"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1428,138 +1428,6 @@
       <c r="A152" t="str">
         <f>IF(About!$A$9+ROW(A150)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A150))</f>
         <v>Vintage2100</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" t="str">
-        <f>IF(About!$A$9+ROW(A151)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A151))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" t="str">
-        <f>IF(About!$A$9+ROW(A152)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A152))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" t="str">
-        <f>IF(About!$A$9+ROW(A153)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A153))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" t="str">
-        <f>IF(About!$A$9+ROW(A154)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A154))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" t="str">
-        <f>IF(About!$A$9+ROW(A155)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A155))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" t="str">
-        <f>IF(About!$A$9+ROW(A156)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A156))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" t="str">
-        <f>IF(About!$A$9+ROW(A157)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A157))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" t="str">
-        <f>IF(About!$A$9+ROW(A158)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A158))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" t="str">
-        <f>IF(About!$A$9+ROW(A159)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A159))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" t="str">
-        <f>IF(About!$A$9+ROW(A160)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A160))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" t="str">
-        <f>IF(About!$A$9+ROW(A161)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A161))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" t="str">
-        <f>IF(About!$A$9+ROW(A162)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A162))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" t="str">
-        <f>IF(About!$A$9+ROW(A163)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A163))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" t="str">
-        <f>IF(About!$A$9+ROW(A164)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A164))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" t="str">
-        <f>IF(About!$A$9+ROW(A165)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A165))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" t="str">
-        <f>IF(About!$A$9+ROW(A166)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A166))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" t="str">
-        <f>IF(About!$A$9+ROW(A167)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A167))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" t="str">
-        <f>IF(About!$A$9+ROW(A168)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A168))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" t="str">
-        <f>IF(About!$A$9+ROW(A169)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A169))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" t="str">
-        <f>IF(About!$A$9+ROW(A170)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A170))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" t="str">
-        <f>IF(About!$A$9+ROW(A171)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A171))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" t="str">
-        <f>IF(About!$A$9+ROW(A172)&gt;About!$A$10,"","Vintage"&amp;About!$A$9+ROW(A172))</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1596,7 +1464,7 @@
   <sheetPr>
     <tabColor theme="3" tint="9.9978637043366805E-2"/>
   </sheetPr>
-  <dimension ref="A1:A173"/>
+  <dimension ref="A1:A151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2502,138 +2370,6 @@
       <c r="A151" t="str">
         <f>V!A152</f>
         <v>Vintage2100</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" t="str">
-        <f>V!A153</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" t="str">
-        <f>V!A154</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" t="str">
-        <f>V!A155</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" t="str">
-        <f>V!A156</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" t="str">
-        <f>V!A157</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" t="str">
-        <f>V!A158</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" t="str">
-        <f>V!A159</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" t="str">
-        <f>V!A160</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" t="str">
-        <f>V!A161</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" t="str">
-        <f>V!A162</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" t="str">
-        <f>V!A163</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" t="str">
-        <f>V!A164</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" t="str">
-        <f>V!A165</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" t="str">
-        <f>V!A166</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" t="str">
-        <f>V!A167</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" t="str">
-        <f>V!A168</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" t="str">
-        <f>V!A169</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" t="str">
-        <f>V!A170</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" t="str">
-        <f>V!A171</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" t="str">
-        <f>V!A172</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" t="str">
-        <f>V!A173</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" t="str">
-        <f>V!A174</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -2646,7 +2382,7 @@
   <sheetPr>
     <tabColor theme="3" tint="9.9978637043366805E-2"/>
   </sheetPr>
-  <dimension ref="A1:A252"/>
+  <dimension ref="A1:A151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -3552,612 +3288,6 @@
       <c r="A151" t="str">
         <f>IF(V!A152="","",V!A151)</f>
         <v>Vintage2099</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" t="str">
-        <f>IF(V!A153="","",V!A152)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" t="str">
-        <f>IF(V!A154="","",V!A153)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" t="str">
-        <f>IF(V!A155="","",V!A154)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" t="str">
-        <f>IF(V!A156="","",V!A155)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" t="str">
-        <f>IF(V!A157="","",V!A156)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" t="str">
-        <f>IF(V!A158="","",V!A157)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" t="str">
-        <f>IF(V!A159="","",V!A158)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" t="str">
-        <f>IF(V!A160="","",V!A159)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" t="str">
-        <f>IF(V!A161="","",V!A160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" t="str">
-        <f>IF(V!A162="","",V!A161)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" t="str">
-        <f>IF(V!A163="","",V!A162)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" t="str">
-        <f>IF(V!A164="","",V!A163)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" t="str">
-        <f>IF(V!A165="","",V!A164)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" t="str">
-        <f>IF(V!A166="","",V!A165)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" t="str">
-        <f>IF(V!A167="","",V!A166)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" t="str">
-        <f>IF(V!A168="","",V!A167)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" t="str">
-        <f>IF(V!A169="","",V!A168)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" t="str">
-        <f>IF(V!A170="","",V!A169)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" t="str">
-        <f>IF(V!A171="","",V!A170)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" t="str">
-        <f>IF(V!A172="","",V!A171)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" t="str">
-        <f>IF(V!A173="","",V!A172)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" t="str">
-        <f>IF(V!A174="","",V!A173)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" t="str">
-        <f>IF(V!A175="","",V!A174)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" t="str">
-        <f>IF(V!A176="","",V!A175)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" t="str">
-        <f>IF(V!A177="","",V!A176)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" t="str">
-        <f>IF(V!A178="","",V!A177)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" t="str">
-        <f>IF(V!A179="","",V!A178)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" t="str">
-        <f>IF(V!A180="","",V!A179)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" t="str">
-        <f>IF(V!A181="","",V!A180)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" t="str">
-        <f>IF(V!A182="","",V!A181)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" t="str">
-        <f>IF(V!A183="","",V!A182)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" t="str">
-        <f>IF(V!A184="","",V!A183)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" t="str">
-        <f>IF(V!A185="","",V!A184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" t="str">
-        <f>IF(V!A186="","",V!A185)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" t="str">
-        <f>IF(V!A187="","",V!A186)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" t="str">
-        <f>IF(V!A188="","",V!A187)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" t="str">
-        <f>IF(V!A189="","",V!A188)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" t="str">
-        <f>IF(V!A190="","",V!A189)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" t="str">
-        <f>IF(V!A191="","",V!A190)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" t="str">
-        <f>IF(V!A192="","",V!A191)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" t="str">
-        <f>IF(V!A193="","",V!A192)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" t="str">
-        <f>IF(V!A194="","",V!A193)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" t="str">
-        <f>IF(V!A195="","",V!A194)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" t="str">
-        <f>IF(V!A196="","",V!A195)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" t="str">
-        <f>IF(V!A197="","",V!A196)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" t="str">
-        <f>IF(V!A198="","",V!A197)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" t="str">
-        <f>IF(V!A199="","",V!A198)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" t="str">
-        <f>IF(V!A200="","",V!A199)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" t="str">
-        <f>IF(V!A201="","",V!A200)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" t="str">
-        <f>IF(V!A202="","",V!A201)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" t="str">
-        <f>IF(V!A203="","",V!A202)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" t="str">
-        <f>IF(V!A204="","",V!A203)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" t="str">
-        <f>IF(V!A205="","",V!A204)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" t="str">
-        <f>IF(V!A206="","",V!A205)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" t="str">
-        <f>IF(V!A207="","",V!A206)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A207" t="str">
-        <f>IF(V!A208="","",V!A207)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" t="str">
-        <f>IF(V!A209="","",V!A208)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209" t="str">
-        <f>IF(V!A210="","",V!A209)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A210" t="str">
-        <f>IF(V!A211="","",V!A210)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A211" t="str">
-        <f>IF(V!A212="","",V!A211)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A212" t="str">
-        <f>IF(V!A213="","",V!A212)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" t="str">
-        <f>IF(V!A214="","",V!A213)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A214" t="str">
-        <f>IF(V!A215="","",V!A214)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A215" t="str">
-        <f>IF(V!A216="","",V!A215)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" t="str">
-        <f>IF(V!A217="","",V!A216)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A217" t="str">
-        <f>IF(V!A218="","",V!A217)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" t="str">
-        <f>IF(V!A219="","",V!A218)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" t="str">
-        <f>IF(V!A220="","",V!A219)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220" t="str">
-        <f>IF(V!A221="","",V!A220)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A221" t="str">
-        <f>IF(V!A222="","",V!A221)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222" t="str">
-        <f>IF(V!A223="","",V!A222)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" t="str">
-        <f>IF(V!A224="","",V!A223)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A224" t="str">
-        <f>IF(V!A225="","",V!A224)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" t="str">
-        <f>IF(V!A226="","",V!A225)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226" t="str">
-        <f>IF(V!A227="","",V!A226)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" t="str">
-        <f>IF(V!A228="","",V!A227)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" t="str">
-        <f>IF(V!A229="","",V!A228)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" t="str">
-        <f>IF(V!A230="","",V!A229)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" t="str">
-        <f>IF(V!A231="","",V!A230)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" t="str">
-        <f>IF(V!A232="","",V!A231)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" t="str">
-        <f>IF(V!A233="","",V!A232)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" t="str">
-        <f>IF(V!A234="","",V!A233)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A234" t="str">
-        <f>IF(V!A235="","",V!A234)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235" t="str">
-        <f>IF(V!A236="","",V!A235)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" t="str">
-        <f>IF(V!A237="","",V!A236)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A237" t="str">
-        <f>IF(V!A238="","",V!A237)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A238" t="str">
-        <f>IF(V!A239="","",V!A238)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" t="str">
-        <f>IF(V!A240="","",V!A239)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" t="str">
-        <f>IF(V!A241="","",V!A240)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241" t="str">
-        <f>IF(V!A242="","",V!A241)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242" t="str">
-        <f>IF(V!A243="","",V!A242)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" t="str">
-        <f>IF(V!A244="","",V!A243)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" t="str">
-        <f>IF(V!A245="","",V!A244)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" t="str">
-        <f>IF(V!A246="","",V!A245)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" t="str">
-        <f>IF(V!A247="","",V!A246)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247" t="str">
-        <f>IF(V!A248="","",V!A247)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" t="str">
-        <f>IF(V!A249="","",V!A248)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A249" t="str">
-        <f>IF(V!A250="","",V!A249)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250" t="str">
-        <f>IF(V!A251="","",V!A250)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A251" t="str">
-        <f>IF(V!A252="","",V!A251)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A252" t="str">
-        <f>IF(V!A253="","",V!A252)</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -4170,7 +3300,7 @@
   <sheetPr>
     <tabColor theme="3" tint="9.9978637043366805E-2"/>
   </sheetPr>
-  <dimension ref="A1:A94"/>
+  <dimension ref="A1:A72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -4603,138 +3733,6 @@
         <v>Vintage2020</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="str">
-        <f>V!A153</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="str">
-        <f>V!A154</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="str">
-        <f>V!A155</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="str">
-        <f>V!A156</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="str">
-        <f>V!A157</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="str">
-        <f>V!A158</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="str">
-        <f>V!A159</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="str">
-        <f>V!A160</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="str">
-        <f>V!A161</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="str">
-        <f>V!A162</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="str">
-        <f>V!A163</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="str">
-        <f>V!A164</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="str">
-        <f>V!A165</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="str">
-        <f>V!A166</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="str">
-        <f>V!A167</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="str">
-        <f>V!A168</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="str">
-        <f>V!A169</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="str">
-        <f>V!A170</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="str">
-        <f>V!A171</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="str">
-        <f>V!A172</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="str">
-        <f>V!A173</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="str">
-        <f>V!A174</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/InputData/plcy-schd/V/Vintage.xlsx
+++ b/InputData/plcy-schd/V/Vintage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\plcy-schd\V\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7A55AB-7E12-459F-B36D-DB5D5E1386B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD12AEC6-80C9-4241-9904-9376C77E7216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11175" activeTab="1" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
+    <workbookView xWindow="29925" yWindow="1125" windowWidth="21600" windowHeight="11175" activeTab="5" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
